--- a/artfynd/S om Kvarntjärnen artfynd.xlsx
+++ b/artfynd/S om Kvarntjärnen artfynd.xlsx
@@ -7535,14 +7535,14 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Bilder, ska mikroskoperas</t>
+          <t>Bilder, ska mikroskoperas. Mycket små porer, ljusgul i kontrast med brunlila zoner, ställen där det är cirkelrunda "hål", tydlig Skeletocutis-doft. Uppdat. 2026-07-26, kollad i mikroskop av undertecknad. Sporerna stämmer bra för lusporing och dåligt för alla de förväxlingsarter jag kan komma på. Sporerna förefaller vara nästan klotrunda till ellipsoida, och de förväxlingsarter jag kommer på (biguttulata, papyracea, stellae, kuehneri) har alla m.e.m. korvformiga sporer. Kollekt sparas, vore bra om någon med mer erfarenhet vid mikroskopet också tog en titt.</t>
         </is>
       </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">

--- a/artfynd/S om Kvarntjärnen artfynd.xlsx
+++ b/artfynd/S om Kvarntjärnen artfynd.xlsx
@@ -7548,6 +7548,31 @@
       <c r="AG60" t="b">
         <v>0</v>
       </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>Låga, kelo. Ur sprickor i veden</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Låga, kelo. Ur sprickor i veden</t>
+        </is>
+      </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>

--- a/artfynd/S om Kvarntjärnen artfynd.xlsx
+++ b/artfynd/S om Kvarntjärnen artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY83"/>
+  <dimension ref="A1:AZ83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297975</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293045</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,6 +1041,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295311</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1137,6 +1157,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295315</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1248,6 +1273,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297957</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1359,6 +1389,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298689</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1468,6 +1503,11 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298697</t>
         </is>
       </c>
     </row>
@@ -1585,6 +1625,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293489</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1696,6 +1741,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297964</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1807,6 +1857,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297966</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1916,6 +1971,11 @@
       <c r="AY12" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298699</t>
         </is>
       </c>
     </row>
@@ -2033,6 +2093,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293448</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2142,6 +2207,11 @@
       <c r="AY14" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295316</t>
         </is>
       </c>
     </row>
@@ -2259,6 +2329,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135296932</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2370,6 +2445,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297958</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2481,6 +2561,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297971</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2592,6 +2677,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297972</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2703,6 +2793,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298698</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2828,6 +2923,11 @@
       <c r="AY20" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293281</t>
         </is>
       </c>
     </row>
@@ -2945,6 +3045,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293771</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3061,6 +3166,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295312</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3172,6 +3282,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298696</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3283,6 +3398,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298701</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3394,6 +3514,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298703</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3505,6 +3630,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298694</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3617,6 +3747,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295321</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3728,6 +3863,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135299062</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3839,6 +3979,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135299064</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3948,6 +4093,11 @@
       <c r="AY30" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135299067</t>
         </is>
       </c>
     </row>
@@ -4065,6 +4215,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293178</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4176,6 +4331,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297962</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4287,6 +4447,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297969</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4398,6 +4563,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298693</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4509,6 +4679,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298705</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4620,6 +4795,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135299060</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4731,6 +4911,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297960</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4867,6 +5052,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295320</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4997,6 +5187,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295324</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5127,6 +5322,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295325</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5257,6 +5457,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295326</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5387,6 +5592,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295327</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5517,6 +5727,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295328</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5647,6 +5862,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295329</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5777,6 +5997,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295330</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5907,6 +6132,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295331</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6038,6 +6268,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295332</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6162,6 +6397,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297970</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6286,6 +6526,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297965</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6410,6 +6655,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297967</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6529,6 +6779,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297973</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6645,6 +6900,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135299063</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6761,6 +7021,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135299065</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6872,6 +7137,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297961</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7000,6 +7270,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297968</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7111,6 +7386,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295298</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7222,6 +7502,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297963</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7333,6 +7618,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135299061</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7442,6 +7732,11 @@
       <c r="AY59" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135299066</t>
         </is>
       </c>
     </row>
@@ -7589,6 +7884,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135297959</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7731,6 +8031,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293128</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7842,6 +8147,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295304</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7954,6 +8264,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295306</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8065,6 +8380,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295307</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8176,6 +8496,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295308</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8287,6 +8612,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295309</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8398,6 +8728,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295310</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8509,6 +8844,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295314</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8620,6 +8960,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295317</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8731,6 +9076,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295318</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8840,6 +9190,11 @@
       <c r="AY71" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295319</t>
         </is>
       </c>
     </row>
@@ -8957,6 +9312,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295322</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9066,6 +9426,11 @@
       <c r="AY73" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295323</t>
         </is>
       </c>
     </row>
@@ -9183,6 +9548,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135296933</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9294,6 +9664,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298690</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9405,6 +9780,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298691</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9516,6 +9896,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298692</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9627,6 +10012,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298695</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9738,6 +10128,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298702</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9849,6 +10244,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298704</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9960,6 +10360,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298706</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10076,6 +10481,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295301</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10187,8 +10597,97 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295302</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S om Kvarntjärnen artfynd.xlsx
+++ b/artfynd/S om Kvarntjärnen artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135297975</v>
       </c>
       <c r="B2" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135293045</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>135295311</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>135295315</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>135297957</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>135298689</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>135298697</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>135293489</v>
       </c>
       <c r="B9" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>135297964</v>
       </c>
       <c r="B10" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>135297966</v>
       </c>
       <c r="B11" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>135298699</v>
       </c>
       <c r="B12" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>135293448</v>
       </c>
       <c r="B13" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>135295316</v>
       </c>
       <c r="B14" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>135296932</v>
       </c>
       <c r="B15" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>135297958</v>
       </c>
       <c r="B16" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>135297971</v>
       </c>
       <c r="B17" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>135297972</v>
       </c>
       <c r="B18" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>135298698</v>
       </c>
       <c r="B19" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>135293281</v>
       </c>
       <c r="B20" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>135293771</v>
       </c>
       <c r="B21" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>135295312</v>
       </c>
       <c r="B22" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>135298696</v>
       </c>
       <c r="B23" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>135298701</v>
       </c>
       <c r="B24" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>135298703</v>
       </c>
       <c r="B25" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>135298694</v>
       </c>
       <c r="B26" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>135295321</v>
       </c>
       <c r="B27" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>135299062</v>
       </c>
       <c r="B28" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>135299064</v>
       </c>
       <c r="B29" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>135299067</v>
       </c>
       <c r="B30" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>135293178</v>
       </c>
       <c r="B31" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>135297962</v>
       </c>
       <c r="B32" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>135297969</v>
       </c>
       <c r="B33" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>135298693</v>
       </c>
       <c r="B34" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>135298705</v>
       </c>
       <c r="B35" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>135299060</v>
       </c>
       <c r="B36" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>135297960</v>
       </c>
       <c r="B37" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>135295320</v>
       </c>
       <c r="B38" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>135295324</v>
       </c>
       <c r="B39" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>135295325</v>
       </c>
       <c r="B40" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>135295326</v>
       </c>
       <c r="B41" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>135295327</v>
       </c>
       <c r="B42" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>135295328</v>
       </c>
       <c r="B43" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>135295329</v>
       </c>
       <c r="B44" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>135295330</v>
       </c>
       <c r="B45" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>135295331</v>
       </c>
       <c r="B46" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>135295332</v>
       </c>
       <c r="B47" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>135297970</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>135297965</v>
       </c>
       <c r="B49" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>135297967</v>
       </c>
       <c r="B50" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>135297973</v>
       </c>
       <c r="B51" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>135299063</v>
       </c>
       <c r="B52" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>135299065</v>
       </c>
       <c r="B53" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>135297961</v>
       </c>
       <c r="B54" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>135297968</v>
       </c>
       <c r="B55" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>135295298</v>
       </c>
       <c r="B56" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>135297963</v>
       </c>
       <c r="B57" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>135299061</v>
       </c>
       <c r="B58" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>135299066</v>
       </c>
       <c r="B59" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>135297959</v>
       </c>
       <c r="B60" t="n">
-        <v>92325</v>
+        <v>92367</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>135293128</v>
       </c>
       <c r="B61" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>135295304</v>
       </c>
       <c r="B62" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>135295306</v>
       </c>
       <c r="B63" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>135295307</v>
       </c>
       <c r="B64" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>135295308</v>
       </c>
       <c r="B65" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>135295309</v>
       </c>
       <c r="B66" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>135295310</v>
       </c>
       <c r="B67" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>135295314</v>
       </c>
       <c r="B68" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>135295317</v>
       </c>
       <c r="B69" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>135295318</v>
       </c>
       <c r="B70" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>135295319</v>
       </c>
       <c r="B71" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>135295322</v>
       </c>
       <c r="B72" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>135295323</v>
       </c>
       <c r="B73" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>135296933</v>
       </c>
       <c r="B74" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>135298690</v>
       </c>
       <c r="B75" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>135298691</v>
       </c>
       <c r="B76" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>135298692</v>
       </c>
       <c r="B77" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>135298695</v>
       </c>
       <c r="B78" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>135298702</v>
       </c>
       <c r="B79" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>135298704</v>
       </c>
       <c r="B80" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         <v>135298706</v>
       </c>
       <c r="B81" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>135295301</v>
       </c>
       <c r="B82" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>135295302</v>
       </c>
       <c r="B83" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/S om Kvarntjärnen artfynd.xlsx
+++ b/artfynd/S om Kvarntjärnen artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>135293045</v>
       </c>
       <c r="B3" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         <v>135295311</v>
       </c>
       <c r="B4" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>135295315</v>
       </c>
       <c r="B5" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>135297957</v>
       </c>
       <c r="B6" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>135298689</v>
       </c>
       <c r="B7" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>135298697</v>
       </c>
       <c r="B8" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>135293489</v>
       </c>
       <c r="B9" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>135297964</v>
       </c>
       <c r="B10" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>135297966</v>
       </c>
       <c r="B11" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>135298699</v>
       </c>
       <c r="B12" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>135293448</v>
       </c>
       <c r="B13" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>135295316</v>
       </c>
       <c r="B14" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>135296932</v>
       </c>
       <c r="B15" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>135297958</v>
       </c>
       <c r="B16" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>135297971</v>
       </c>
       <c r="B17" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>135297972</v>
       </c>
       <c r="B18" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>135298698</v>
       </c>
       <c r="B19" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>135293281</v>
       </c>
       <c r="B20" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>135293771</v>
       </c>
       <c r="B21" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>135295312</v>
       </c>
       <c r="B22" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>135298696</v>
       </c>
       <c r="B23" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>135298701</v>
       </c>
       <c r="B24" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>135298703</v>
       </c>
       <c r="B25" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>135298694</v>
       </c>
       <c r="B26" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>135295321</v>
       </c>
       <c r="B27" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>135299062</v>
       </c>
       <c r="B28" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>135299064</v>
       </c>
       <c r="B29" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>135299067</v>
       </c>
       <c r="B30" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>135293178</v>
       </c>
       <c r="B31" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>135297962</v>
       </c>
       <c r="B32" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>135297969</v>
       </c>
       <c r="B33" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>135298693</v>
       </c>
       <c r="B34" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>135298705</v>
       </c>
       <c r="B35" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>135299060</v>
       </c>
       <c r="B36" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>135297960</v>
       </c>
       <c r="B37" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>135295298</v>
       </c>
       <c r="B56" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>135297963</v>
       </c>
       <c r="B57" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>135299061</v>
       </c>
       <c r="B58" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>135299066</v>
       </c>
       <c r="B59" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>135297959</v>
       </c>
       <c r="B60" t="n">
-        <v>92367</v>
+        <v>92394</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>135293128</v>
       </c>
       <c r="B61" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>135295304</v>
       </c>
       <c r="B62" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>135295306</v>
       </c>
       <c r="B63" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>135295307</v>
       </c>
       <c r="B64" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>135295308</v>
       </c>
       <c r="B65" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>135295309</v>
       </c>
       <c r="B66" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>135295310</v>
       </c>
       <c r="B67" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>135295314</v>
       </c>
       <c r="B68" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>135295317</v>
       </c>
       <c r="B69" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>135295318</v>
       </c>
       <c r="B70" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>135295319</v>
       </c>
       <c r="B71" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>135295322</v>
       </c>
       <c r="B72" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>135295323</v>
       </c>
       <c r="B73" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>135296933</v>
       </c>
       <c r="B74" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>135298690</v>
       </c>
       <c r="B75" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>135298691</v>
       </c>
       <c r="B76" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>135298692</v>
       </c>
       <c r="B77" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>135298695</v>
       </c>
       <c r="B78" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>135298702</v>
       </c>
       <c r="B79" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>135298704</v>
       </c>
       <c r="B80" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         <v>135298706</v>
       </c>
       <c r="B81" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>135295301</v>
       </c>
       <c r="B82" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>135295302</v>
       </c>
       <c r="B83" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/S om Kvarntjärnen artfynd.xlsx
+++ b/artfynd/S om Kvarntjärnen artfynd.xlsx
@@ -1516,7 +1516,7 @@
         <v>135293489</v>
       </c>
       <c r="B9" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>135297964</v>
       </c>
       <c r="B10" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>135297966</v>
       </c>
       <c r="B11" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>135298699</v>
       </c>
       <c r="B12" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>135293448</v>
       </c>
       <c r="B13" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>135295316</v>
       </c>
       <c r="B14" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>135296932</v>
       </c>
       <c r="B15" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>135297958</v>
       </c>
       <c r="B16" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>135297971</v>
       </c>
       <c r="B17" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>135297972</v>
       </c>
       <c r="B18" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>135298698</v>
       </c>
       <c r="B19" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>135293281</v>
       </c>
       <c r="B20" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>135293771</v>
       </c>
       <c r="B21" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>135295312</v>
       </c>
       <c r="B22" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>135298696</v>
       </c>
       <c r="B23" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>135298701</v>
       </c>
       <c r="B24" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>135298703</v>
       </c>
       <c r="B25" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>135298694</v>
       </c>
       <c r="B26" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>135295298</v>
       </c>
       <c r="B56" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>135297963</v>
       </c>
       <c r="B57" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>135299061</v>
       </c>
       <c r="B58" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>135299066</v>
       </c>
       <c r="B59" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>135297959</v>
       </c>
       <c r="B60" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>135295301</v>
       </c>
       <c r="B82" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/S om Kvarntjärnen artfynd.xlsx
+++ b/artfynd/S om Kvarntjärnen artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135297975</v>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>135297970</v>
       </c>
       <c r="B48" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>135297959</v>
       </c>
       <c r="B60" t="n">
-        <v>92401</v>
+        <v>92413</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
